--- a/FI.xlsx
+++ b/FI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD7CDA5-9EFE-4B4F-BA2D-A3C8BBE24CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2458F47B-561F-4E6E-BC0F-DA5B0F43E985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{8871E1AF-CC88-4971-9D46-707769305EE3}"/>
+    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" xr2:uid="{8871E1AF-CC88-4971-9D46-707769305EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>33615.742937499999</v>
+        <v>29904.564917200001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -723,7 +723,7 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>62746.742937499999</v>
+        <v>59035.564917199998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1548,7 +1548,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="12">
-        <f t="shared" ref="C16:I16" si="5">+C13-C14+C15</f>
+        <f t="shared" ref="C16:H16" si="5">+C13-C14+C15</f>
         <v>1181</v>
       </c>
       <c r="D16" s="12">
@@ -1731,7 +1731,7 @@
         <v>36</v>
       </c>
       <c r="C19" s="12">
-        <f t="shared" ref="C19:I19" si="8">+C16-C17-C18</f>
+        <f t="shared" ref="C19:H19" si="8">+C16-C17-C18</f>
         <v>913</v>
       </c>
       <c r="D19" s="12">
@@ -1914,7 +1914,7 @@
         <v>39</v>
       </c>
       <c r="C22" s="12">
-        <f t="shared" ref="C22:I22" si="11">+C19-C20+C21</f>
+        <f t="shared" ref="C22:H22" si="11">+C19-C20+C21</f>
         <v>752</v>
       </c>
       <c r="D22" s="12">
@@ -2373,7 +2373,7 @@
         <v>50</v>
       </c>
       <c r="C32" s="14">
-        <f t="shared" ref="C32:I32" si="20">+(C8-C11)/C8</f>
+        <f t="shared" ref="C32:H32" si="20">+(C8-C11)/C8</f>
         <v>0.66149999999999998</v>
       </c>
       <c r="D32" s="14">
@@ -2421,7 +2421,7 @@
         <v>51</v>
       </c>
       <c r="C33" s="14">
-        <f t="shared" ref="C33:I33" si="21">+(C9-C12)/C9</f>
+        <f t="shared" ref="C33:H33" si="21">+(C9-C12)/C9</f>
         <v>0.26274065685164211</v>
       </c>
       <c r="D33" s="14">
@@ -2469,7 +2469,7 @@
         <v>52</v>
       </c>
       <c r="C34" s="14">
-        <f t="shared" ref="C34:I34" si="22">+C13/C10</f>
+        <f t="shared" ref="C34:H34" si="22">+C13/C10</f>
         <v>0.58939176735613352</v>
       </c>
       <c r="D34" s="14">
@@ -2517,7 +2517,7 @@
         <v>53</v>
       </c>
       <c r="C35" s="14">
-        <f t="shared" ref="C35:I35" si="23">+C16/C10</f>
+        <f t="shared" ref="C35:H35" si="23">+C16/C10</f>
         <v>0.24185951259471636</v>
       </c>
       <c r="D35" s="14">
@@ -2565,7 +2565,7 @@
         <v>54</v>
       </c>
       <c r="C36" s="14">
-        <f t="shared" ref="C36:I36" si="24">+C20/C19</f>
+        <f t="shared" ref="C36:H36" si="24">+C20/C19</f>
         <v>0.16757940854326397</v>
       </c>
       <c r="D36" s="14">

--- a/FI.xlsx
+++ b/FI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2458F47B-561F-4E6E-BC0F-DA5B0F43E985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979670AD-B9E5-468E-8733-BE09FE8992A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="5070" windowWidth="38175" windowHeight="15240" xr2:uid="{8871E1AF-CC88-4971-9D46-707769305EE3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8871E1AF-CC88-4971-9D46-707769305EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>Fiserv</t>
   </si>
@@ -206,6 +206,9 @@
   <si>
     <t>Revenue Growth</t>
   </si>
+  <si>
+    <t>FISV</t>
+  </si>
 </sst>
 </file>
 
@@ -215,13 +218,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\-#,##0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -291,30 +300,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="39" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -671,7 +681,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>55.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -686,12 +696,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>29904.564917200001</v>
+        <v>27269.090670900005</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -723,7 +736,7 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>59035.564917199998</v>
+        <v>56400.090670900005</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
